--- a/output/pdf_financials_xlsx/PDV.xlsx
+++ b/output/pdf_financials_xlsx/PDV.xlsx
@@ -2113,40 +2113,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.69349</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.999263</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.833185</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.568345</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.839499</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.496485</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.190368</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.85969</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.250603</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.507899</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.300174</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.7513030000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2199,40 +2199,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.69349</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.999263</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.833185</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.568345</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.839499</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.496485</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.190368</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.85969</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.250603</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.507899</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.300174</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.7513030000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2724,31 +2724,31 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>27.658537</v>
+        <v>24.090192</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>25.84745</v>
+        <v>25.007951</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>22.453726</v>
+        <v>20.957241</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>24.054815</v>
+        <v>22.864447</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>21.335318</v>
+        <v>20.475628</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>18.305959</v>
+        <v>17.055356</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>16.618378</v>
+        <v>16.110479</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>15.46157</v>
+        <v>15.161396</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>13.586854</v>
+        <v>12.835551</v>
       </c>
     </row>
     <row r="49">
@@ -6988,7 +6988,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">

--- a/output/pdf_financials_xlsx/PDV.xlsx
+++ b/output/pdf_financials_xlsx/PDV.xlsx
@@ -712,40 +712,40 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.27691</v>
+        <v>0.297137</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.271549</v>
+        <v>0.291219</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.232398</v>
+        <v>0.252858</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.238531</v>
+        <v>0.259991</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.246447</v>
+        <v>0.27003</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.224795</v>
+        <v>0.248378</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.207002</v>
+        <v>0.230585</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.204985</v>
+        <v>0.228568</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.191212</v>
+        <v>0.214795</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.165298</v>
+        <v>0.188881</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.152477</v>
+        <v>0.17606</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.150564</v>
+        <v>0.172589</v>
       </c>
     </row>
     <row r="8">
@@ -5760,40 +5760,40 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>5.576625</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>8.653824</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>11.717935</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>15.59693</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>7.935505</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>2.327427</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>1.610914</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>6.632664</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>1.550006</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>3.950153</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>2.562795</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>1.38202</v>
       </c>
     </row>
     <row r="116">
@@ -6455,40 +6455,26 @@
       <c r="F130" s="3" t="n">
         <v>3.568345</v>
       </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G130" s="3" t="n">
+        <v>0.839499</v>
+      </c>
+      <c r="H130" s="3" t="n">
+        <v>1.496485</v>
+      </c>
+      <c r="I130" s="3" t="n">
+        <v>1.190368</v>
+      </c>
+      <c r="J130" s="3" t="n">
+        <v>0.85969</v>
+      </c>
+      <c r="K130" s="3" t="n">
+        <v>1.250603</v>
+      </c>
+      <c r="L130" s="3" t="n">
+        <v>0.946702</v>
+      </c>
+      <c r="M130" s="3" t="n">
+        <v>0.300174</v>
       </c>
     </row>
     <row r="131">
@@ -6598,40 +6584,26 @@
       <c r="F133" s="3" t="n">
         <v>0.839499</v>
       </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G133" s="3" t="n">
+        <v>1.496485</v>
+      </c>
+      <c r="H133" s="3" t="n">
+        <v>1.190368</v>
+      </c>
+      <c r="I133" s="3" t="n">
+        <v>0.85969</v>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>1.250603</v>
+      </c>
+      <c r="K133" s="3" t="n">
+        <v>0.507899</v>
+      </c>
+      <c r="L133" s="3" t="n">
+        <v>0.300174</v>
+      </c>
+      <c r="M133" s="3" t="n">
+        <v>0.7513030000000001</v>
       </c>
     </row>
     <row r="134">
@@ -12214,7 +12186,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -12898,7 +12874,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -12972,7 +12952,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -16500,7 +16484,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>
@@ -17124,7 +17112,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -17192,7 +17184,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -26882,7 +26878,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -26956,7 +26956,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E279" t="inlineStr">
         <is>
           <t>-</t>
@@ -29594,7 +29598,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E315" s="5" t="n">
         <v>5.576625</v>
       </c>
@@ -40888,7 +40896,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E469" t="inlineStr">
         <is>
           <t>-</t>
@@ -41454,7 +41466,11 @@
           <t>of redeemable Class A shares before distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E478" t="inlineStr">
         <is>
           <t>-</t>
@@ -41516,7 +41532,11 @@
           <t>Distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
@@ -42394,7 +42414,11 @@
           <t>Director’s fees</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E492" t="inlineStr">
         <is>
           <t>-</t>
@@ -43170,7 +43194,11 @@
           <t>Net investment income before distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E503" s="5" t="n">
         <v>0.840069</v>
       </c>
@@ -43238,7 +43266,11 @@
           <t>Distributions on Preferred shares (note 4 and 7)</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E504" s="5" t="n">
         <v>-0.872468</v>
       </c>
@@ -44738,7 +44770,11 @@
           <t>Directors’ fees</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E525" s="5" t="n">
         <v>0.020227</v>
       </c>
@@ -45312,7 +45348,11 @@
           <t>Distributions on Preferred shares (note 4 and 8)</t>
         </is>
       </c>
-      <c r="D533" t="inlineStr"/>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E533" t="inlineStr">
         <is>
           <t>-</t>
